--- a/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_Link_Ax3.xlsx
+++ b/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_Link_Ax3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\Subframe_Conn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24FBC20-0727-4C50-8DBA-E0C4AD4CC180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA350F5-8F4B-40E0-91F6-65A06C49854F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="988" activeTab="1" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
+    <workbookView xWindow="1305" yWindow="720" windowWidth="25545" windowHeight="10215" tabRatio="988" activeTab="1" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
   </bookViews>
   <sheets>
     <sheet name="BUJAx3_SLGf_S2LAF_LAF" sheetId="54" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="37">
   <si>
     <t>Units</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>BushLink_Ax3_SLGf_S2LAF_LAR</t>
+  </si>
+  <si>
+    <t>AxisAttachment</t>
+  </si>
+  <si>
+    <t>Outer</t>
   </si>
 </sst>
 </file>
@@ -607,7 +613,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
@@ -626,7 +632,7 @@
     <col min="19" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -646,7 +652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -659,7 +665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>19</v>
       </c>
@@ -673,7 +679,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -688,7 +694,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>30</v>
       </c>
@@ -719,7 +725,7 @@
         <v>0.191</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>31</v>
       </c>
@@ -741,816 +747,833 @@
         <v>0.20100000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" s="4"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="E7" s="4" t="s">
+      <c r="C8" s="6"/>
+      <c r="E8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H8" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I9" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J9" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K9" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L9" s="13">
-        <v>0</v>
-      </c>
-      <c r="M9" s="12">
-        <v>1</v>
-      </c>
-      <c r="N9" s="12">
+      <c r="H9" s="10">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="O9" s="12">
-        <v>3</v>
-      </c>
-      <c r="P9" s="13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="12">
-        <f>-4*P33</f>
+        <v>-4</v>
+      </c>
+      <c r="I10" s="13">
+        <v>-3</v>
+      </c>
+      <c r="J10" s="13">
+        <v>-2</v>
+      </c>
+      <c r="K10" s="13">
+        <v>-1</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12">
+        <v>1</v>
+      </c>
+      <c r="N10" s="12">
+        <v>2</v>
+      </c>
+      <c r="O10" s="12">
+        <v>3</v>
+      </c>
+      <c r="P10" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="12">
+        <f>-4*P34</f>
         <v>-4000</v>
       </c>
-      <c r="I10" s="13">
-        <f>-2.75*P33</f>
+      <c r="I11" s="13">
+        <f>-2.75*P34</f>
         <v>-2750</v>
       </c>
-      <c r="J10" s="13">
-        <f>-1.5*P33</f>
+      <c r="J11" s="13">
+        <f>-1.5*P34</f>
         <v>-1500</v>
       </c>
-      <c r="K10" s="13">
-        <f>-0.5*P33</f>
+      <c r="K11" s="13">
+        <f>-0.5*P34</f>
         <v>-500</v>
       </c>
-      <c r="L10" s="13">
-        <f>0*P33</f>
+      <c r="L11" s="13">
+        <f>0*P34</f>
         <v>0</v>
       </c>
-      <c r="M10" s="12">
-        <f>0.5*P33</f>
+      <c r="M11" s="12">
+        <f>0.5*P34</f>
         <v>500</v>
       </c>
-      <c r="N10" s="12">
-        <f>1.5*P33</f>
+      <c r="N11" s="12">
+        <f>1.5*P34</f>
         <v>1500</v>
       </c>
-      <c r="O10" s="12">
-        <f>2.75*P33</f>
+      <c r="O11" s="12">
+        <f>2.75*P34</f>
         <v>2750</v>
       </c>
-      <c r="P10" s="13">
-        <f>4*P33</f>
+      <c r="P11" s="13">
+        <f>4*P34</f>
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="E11" s="4" t="s">
+      <c r="C12" s="6"/>
+      <c r="E12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H12" s="14" t="s">
         <v>7</v>
-      </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10">
-        <v>2000</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I13" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J13" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K13" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L13" s="13">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>1</v>
-      </c>
-      <c r="N13" s="12">
-        <v>2</v>
-      </c>
-      <c r="O13" s="12">
-        <v>3</v>
-      </c>
-      <c r="P13" s="13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="5"/>
+      <c r="H13" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C14" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="12">
-        <f>-4*P37</f>
-        <v>-4000</v>
+        <v>-4</v>
       </c>
       <c r="I14" s="13">
-        <f>-2.75*P37</f>
-        <v>-2750</v>
+        <v>-3</v>
       </c>
       <c r="J14" s="13">
-        <f>-1.5*P37</f>
-        <v>-1500</v>
+        <v>-2</v>
       </c>
       <c r="K14" s="13">
-        <f>-0.5*P37</f>
-        <v>-500</v>
+        <v>-1</v>
       </c>
       <c r="L14" s="13">
-        <f>0*P37</f>
         <v>0</v>
       </c>
       <c r="M14" s="12">
-        <f>0.5*P37</f>
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="N14" s="12">
-        <f>1.5*P37</f>
-        <v>1500</v>
+        <v>2</v>
       </c>
       <c r="O14" s="12">
-        <f>2.75*P37</f>
-        <v>2750</v>
+        <v>3</v>
       </c>
       <c r="P14" s="13">
-        <f>4*P37</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="E15" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="13"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
+      <c r="H15" s="12">
+        <f>-4*P38</f>
+        <v>-4000</v>
+      </c>
+      <c r="I15" s="13">
+        <f>-2.75*P38</f>
+        <v>-2750</v>
+      </c>
+      <c r="J15" s="13">
+        <f>-1.5*P38</f>
+        <v>-1500</v>
+      </c>
+      <c r="K15" s="13">
+        <f>-0.5*P38</f>
+        <v>-500</v>
+      </c>
+      <c r="L15" s="13">
+        <f>0*P38</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="12">
+        <f>0.5*P38</f>
+        <v>500</v>
+      </c>
+      <c r="N15" s="12">
+        <f>1.5*P38</f>
+        <v>1500</v>
+      </c>
+      <c r="O15" s="12">
+        <f>2.75*P38</f>
+        <v>2750</v>
+      </c>
+      <c r="P15" s="13">
+        <f>4*P38</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="B16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="E16" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="10">
-        <v>2000</v>
-      </c>
+      <c r="H16" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I17" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J17" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K17" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L17" s="13">
-        <v>0</v>
-      </c>
-      <c r="M17" s="12">
-        <v>1</v>
-      </c>
-      <c r="N17" s="12">
-        <v>2</v>
-      </c>
-      <c r="O17" s="12">
-        <v>3</v>
-      </c>
-      <c r="P17" s="13">
-        <v>4</v>
+      <c r="H17" s="10">
+        <v>2000</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C18" s="6" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="12">
-        <f>-4*P41</f>
-        <v>-4000</v>
+        <v>-4</v>
       </c>
       <c r="I18" s="13">
-        <f>-2.75*P41</f>
-        <v>-2750</v>
+        <v>-3</v>
       </c>
       <c r="J18" s="13">
-        <f>-1.5*P41</f>
-        <v>-1500</v>
+        <v>-2</v>
       </c>
       <c r="K18" s="13">
-        <f>-0.5*P41</f>
-        <v>-500</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="13">
-        <f>0*P41</f>
         <v>0</v>
       </c>
       <c r="M18" s="12">
-        <f>0.5*P41</f>
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="N18" s="12">
-        <f>1.5*P41</f>
-        <v>1500</v>
+        <v>2</v>
       </c>
       <c r="O18" s="12">
-        <f>2.75*P41</f>
-        <v>2750</v>
+        <v>3</v>
       </c>
       <c r="P18" s="13">
-        <f>4*P41</f>
-        <v>4000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="E19" s="4" t="s">
-        <v>18</v>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="13"/>
+      <c r="H19" s="12">
+        <f>-4*P42</f>
+        <v>-4000</v>
+      </c>
+      <c r="I19" s="13">
+        <f>-2.75*P42</f>
+        <v>-2750</v>
+      </c>
+      <c r="J19" s="13">
+        <f>-1.5*P42</f>
+        <v>-1500</v>
+      </c>
+      <c r="K19" s="13">
+        <f>-0.5*P42</f>
+        <v>-500</v>
+      </c>
+      <c r="L19" s="13">
+        <f>0*P42</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="12">
+        <f>0.5*P42</f>
+        <v>500</v>
+      </c>
+      <c r="N19" s="12">
+        <f>1.5*P42</f>
+        <v>1500</v>
+      </c>
+      <c r="O19" s="12">
+        <f>2.75*P42</f>
+        <v>2750</v>
+      </c>
+      <c r="P19" s="13">
+        <f>4*P42</f>
+        <v>4000</v>
+      </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
+      <c r="A20" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="B20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="E20" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
-      <c r="H20" s="10">
-        <v>2000</v>
+      <c r="H20" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="13"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
-      <c r="H21" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I21" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J21" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K21" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L21" s="13">
-        <v>0</v>
-      </c>
-      <c r="M21" s="12">
-        <v>1</v>
-      </c>
-      <c r="N21" s="12">
-        <v>2</v>
-      </c>
-      <c r="O21" s="12">
-        <v>3</v>
-      </c>
-      <c r="P21" s="13">
-        <v>4</v>
-      </c>
+      <c r="H21" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C22" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="12">
-        <f>-4*P45</f>
-        <v>-4000</v>
+        <v>-4</v>
       </c>
       <c r="I22" s="13">
-        <f>-2.75*P45</f>
-        <v>-2750</v>
+        <v>-3</v>
       </c>
       <c r="J22" s="13">
-        <f>-1.5*P45</f>
-        <v>-1500</v>
+        <v>-2</v>
       </c>
       <c r="K22" s="13">
-        <f>-0.5*P45</f>
-        <v>-500</v>
+        <v>-1</v>
       </c>
       <c r="L22" s="13">
-        <f>0*P45</f>
         <v>0</v>
       </c>
       <c r="M22" s="12">
-        <f>0.5*P45</f>
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="N22" s="12">
-        <f>1.5*P45</f>
-        <v>1500</v>
+        <v>2</v>
       </c>
       <c r="O22" s="12">
-        <f>2.75*P45</f>
-        <v>2750</v>
+        <v>3</v>
       </c>
       <c r="P22" s="13">
-        <f>4*P45</f>
-        <v>4000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="E23" s="4" t="s">
-        <v>18</v>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="13"/>
+      <c r="H23" s="12">
+        <f>-4*P46</f>
+        <v>-4000</v>
+      </c>
+      <c r="I23" s="13">
+        <f>-2.75*P46</f>
+        <v>-2750</v>
+      </c>
+      <c r="J23" s="13">
+        <f>-1.5*P46</f>
+        <v>-1500</v>
+      </c>
+      <c r="K23" s="13">
+        <f>-0.5*P46</f>
+        <v>-500</v>
+      </c>
+      <c r="L23" s="13">
+        <f>0*P46</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="12">
+        <f>0.5*P46</f>
+        <v>500</v>
+      </c>
+      <c r="N23" s="12">
+        <f>1.5*P46</f>
+        <v>1500</v>
+      </c>
+      <c r="O23" s="12">
+        <f>2.75*P46</f>
+        <v>2750</v>
+      </c>
+      <c r="P23" s="13">
+        <f>4*P46</f>
+        <v>4000</v>
+      </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
+      <c r="A24" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="B24" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="E24" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="10">
-        <v>2000</v>
-      </c>
+      <c r="H24" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="13"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I25" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J25" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K25" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L25" s="13">
-        <v>0</v>
-      </c>
-      <c r="M25" s="12">
-        <v>1</v>
-      </c>
-      <c r="N25" s="12">
-        <v>2</v>
-      </c>
-      <c r="O25" s="12">
-        <v>3</v>
-      </c>
-      <c r="P25" s="13">
-        <v>4</v>
+      <c r="H25" s="10">
+        <v>2000</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
+      <c r="B26" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C26" s="6" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="12">
-        <f>-4*P49</f>
-        <v>-4000</v>
+        <v>-4</v>
       </c>
       <c r="I26" s="13">
-        <f>-2.75*P49</f>
-        <v>-2750</v>
+        <v>-3</v>
       </c>
       <c r="J26" s="13">
-        <f>-1.5*P49</f>
-        <v>-1500</v>
+        <v>-2</v>
       </c>
       <c r="K26" s="13">
-        <f>-0.5*P49</f>
-        <v>-500</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="13">
-        <f>0*P49</f>
         <v>0</v>
       </c>
       <c r="M26" s="12">
-        <f>0.5*P49</f>
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="N26" s="12">
-        <f>1.5*P49</f>
-        <v>1500</v>
+        <v>2</v>
       </c>
       <c r="O26" s="12">
-        <f>2.75*P49</f>
-        <v>2750</v>
+        <v>3</v>
       </c>
       <c r="P26" s="13">
-        <f>4*P49</f>
-        <v>4000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="E27" s="4" t="s">
-        <v>18</v>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="H27" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="13"/>
+      <c r="H27" s="12">
+        <f>-4*P50</f>
+        <v>-4000</v>
+      </c>
+      <c r="I27" s="13">
+        <f>-2.75*P50</f>
+        <v>-2750</v>
+      </c>
+      <c r="J27" s="13">
+        <f>-1.5*P50</f>
+        <v>-1500</v>
+      </c>
+      <c r="K27" s="13">
+        <f>-0.5*P50</f>
+        <v>-500</v>
+      </c>
+      <c r="L27" s="13">
+        <f>0*P50</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="12">
+        <f>0.5*P50</f>
+        <v>500</v>
+      </c>
+      <c r="N27" s="12">
+        <f>1.5*P50</f>
+        <v>1500</v>
+      </c>
+      <c r="O27" s="12">
+        <f>2.75*P50</f>
+        <v>2750</v>
+      </c>
+      <c r="P27" s="13">
+        <f>4*P50</f>
+        <v>4000</v>
+      </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
+      <c r="A28" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="B28" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="E28" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="10">
-        <v>2000</v>
+      <c r="H28" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="13"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I29" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J29" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K29" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L29" s="13">
-        <v>0</v>
-      </c>
-      <c r="M29" s="12">
-        <v>1</v>
-      </c>
-      <c r="N29" s="12">
-        <v>2</v>
-      </c>
-      <c r="O29" s="12">
-        <v>3</v>
-      </c>
-      <c r="P29" s="13">
-        <v>4</v>
-      </c>
+      <c r="H29" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
+      <c r="B30" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C30" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="12">
-        <f>-4*P53</f>
+        <v>-4</v>
+      </c>
+      <c r="I30" s="13">
+        <v>-3</v>
+      </c>
+      <c r="J30" s="13">
+        <v>-2</v>
+      </c>
+      <c r="K30" s="13">
+        <v>-1</v>
+      </c>
+      <c r="L30" s="13">
+        <v>0</v>
+      </c>
+      <c r="M30" s="12">
+        <v>1</v>
+      </c>
+      <c r="N30" s="12">
+        <v>2</v>
+      </c>
+      <c r="O30" s="12">
+        <v>3</v>
+      </c>
+      <c r="P30" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="12">
+        <f>-4*P54</f>
         <v>-4000</v>
       </c>
-      <c r="I30" s="13">
-        <f>-2.75*P53</f>
+      <c r="I31" s="13">
+        <f>-2.75*P54</f>
         <v>-2750</v>
       </c>
-      <c r="J30" s="13">
-        <f>-1.5*P53</f>
+      <c r="J31" s="13">
+        <f>-1.5*P54</f>
         <v>-1500</v>
       </c>
-      <c r="K30" s="13">
-        <f>-0.5*P53</f>
+      <c r="K31" s="13">
+        <f>-0.5*P54</f>
         <v>-500</v>
       </c>
-      <c r="L30" s="13">
-        <f>0*P53</f>
+      <c r="L31" s="13">
+        <f>0*P54</f>
         <v>0</v>
       </c>
-      <c r="M30" s="12">
-        <f>0.5*P53</f>
+      <c r="M31" s="12">
+        <f>0.5*P54</f>
         <v>500</v>
       </c>
-      <c r="N30" s="12">
-        <f>1.5*P53</f>
+      <c r="N31" s="12">
+        <f>1.5*P54</f>
         <v>1500</v>
       </c>
-      <c r="O30" s="12">
-        <f>2.75*P53</f>
+      <c r="O31" s="12">
+        <f>2.75*P54</f>
         <v>2750</v>
       </c>
-      <c r="P30" s="13">
-        <f>4*P53</f>
+      <c r="P31" s="13">
+        <f>4*P54</f>
         <v>4000</v>
       </c>
     </row>
-    <row r="33" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P33" s="4">
+    <row r="34" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P34" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P37" s="4">
+    <row r="38" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P38" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="41" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P41" s="4">
+    <row r="42" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P42" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="45" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P45" s="4">
+    <row r="46" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P46" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="49" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P49" s="4">
+    <row r="50" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P50" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="53" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P53" s="4">
+    <row r="54" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P54" s="4">
         <v>1000</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:C10 B12:C30 A21 A29">
+  <conditionalFormatting sqref="B9:C11 B13:C31 A22 A30">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
@@ -1564,7 +1587,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
@@ -1699,158 +1722,154 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="E7" s="4" t="s">
+      <c r="C8" s="6"/>
+      <c r="E8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H8" s="14" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10">
-        <v>2000</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I9" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J9" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K9" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L9" s="13">
-        <v>0</v>
-      </c>
-      <c r="M9" s="12">
-        <v>1</v>
-      </c>
-      <c r="N9" s="12">
-        <v>2</v>
-      </c>
-      <c r="O9" s="12">
-        <v>3</v>
-      </c>
-      <c r="P9" s="13">
-        <v>4</v>
+      <c r="H9" s="10">
+        <v>2000</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C10" s="6" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="12">
-        <f>-4*P33</f>
+        <v>-4</v>
+      </c>
+      <c r="I10" s="13">
+        <v>-3</v>
+      </c>
+      <c r="J10" s="13">
+        <v>-2</v>
+      </c>
+      <c r="K10" s="13">
+        <v>-1</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12">
+        <v>1</v>
+      </c>
+      <c r="N10" s="12">
+        <v>2</v>
+      </c>
+      <c r="O10" s="12">
+        <v>3</v>
+      </c>
+      <c r="P10" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="12">
+        <f>-4*P34</f>
         <v>-4000</v>
       </c>
-      <c r="I10" s="13">
-        <f>-2.75*P33</f>
+      <c r="I11" s="13">
+        <f>-2.75*P34</f>
         <v>-2750</v>
       </c>
-      <c r="J10" s="13">
-        <f>-1.5*P33</f>
+      <c r="J11" s="13">
+        <f>-1.5*P34</f>
         <v>-1500</v>
       </c>
-      <c r="K10" s="13">
-        <f>-0.5*P33</f>
+      <c r="K11" s="13">
+        <f>-0.5*P34</f>
         <v>-500</v>
       </c>
-      <c r="L10" s="13">
-        <f>0*P33</f>
+      <c r="L11" s="13">
+        <f>0*P34</f>
         <v>0</v>
       </c>
-      <c r="M10" s="12">
-        <f>0.5*P33</f>
+      <c r="M11" s="12">
+        <f>0.5*P34</f>
         <v>500</v>
       </c>
-      <c r="N10" s="12">
-        <f>1.5*P33</f>
+      <c r="N11" s="12">
+        <f>1.5*P34</f>
         <v>1500</v>
       </c>
-      <c r="O10" s="12">
-        <f>2.75*P33</f>
+      <c r="O11" s="12">
+        <f>2.75*P34</f>
         <v>2750</v>
       </c>
-      <c r="P10" s="13">
-        <f>4*P33</f>
+      <c r="P11" s="13">
+        <f>4*P34</f>
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="E11" s="4" t="s">
+      <c r="C12" s="6"/>
+      <c r="E12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H12" s="14" t="s">
         <v>7</v>
-      </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10">
-        <v>2000</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
@@ -1859,654 +1878,674 @@
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I13" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J13" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K13" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L13" s="13">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>1</v>
-      </c>
-      <c r="N13" s="12">
-        <v>2</v>
-      </c>
-      <c r="O13" s="12">
-        <v>3</v>
-      </c>
-      <c r="P13" s="13">
-        <v>4</v>
-      </c>
+      <c r="H13" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="5"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C14" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="12">
-        <f>-4*P37</f>
-        <v>-4000</v>
+        <v>-4</v>
       </c>
       <c r="I14" s="13">
-        <f>-2.75*P37</f>
-        <v>-2750</v>
+        <v>-3</v>
       </c>
       <c r="J14" s="13">
-        <f>-1.5*P37</f>
-        <v>-1500</v>
+        <v>-2</v>
       </c>
       <c r="K14" s="13">
-        <f>-0.5*P37</f>
-        <v>-500</v>
+        <v>-1</v>
       </c>
       <c r="L14" s="13">
-        <f>0*P37</f>
         <v>0</v>
       </c>
       <c r="M14" s="12">
-        <f>0.5*P37</f>
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="N14" s="12">
-        <f>1.5*P37</f>
-        <v>1500</v>
+        <v>2</v>
       </c>
       <c r="O14" s="12">
-        <f>2.75*P37</f>
-        <v>2750</v>
+        <v>3</v>
       </c>
       <c r="P14" s="13">
-        <f>4*P37</f>
-        <v>4000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="E15" s="4" t="s">
-        <v>18</v>
+      <c r="A15" s="6"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="13"/>
+      <c r="H15" s="12">
+        <f>-4*P38</f>
+        <v>-4000</v>
+      </c>
+      <c r="I15" s="13">
+        <f>-2.75*P38</f>
+        <v>-2750</v>
+      </c>
+      <c r="J15" s="13">
+        <f>-1.5*P38</f>
+        <v>-1500</v>
+      </c>
+      <c r="K15" s="13">
+        <f>-0.5*P38</f>
+        <v>-500</v>
+      </c>
+      <c r="L15" s="13">
+        <f>0*P38</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="12">
+        <f>0.5*P38</f>
+        <v>500</v>
+      </c>
+      <c r="N15" s="12">
+        <f>1.5*P38</f>
+        <v>1500</v>
+      </c>
+      <c r="O15" s="12">
+        <f>2.75*P38</f>
+        <v>2750</v>
+      </c>
+      <c r="P15" s="13">
+        <f>4*P38</f>
+        <v>4000</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
+      <c r="A16" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="B16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="E16" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="10">
-        <v>2000</v>
-      </c>
+      <c r="H16" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I17" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J17" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K17" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L17" s="13">
-        <v>0</v>
-      </c>
-      <c r="M17" s="12">
-        <v>1</v>
-      </c>
-      <c r="N17" s="12">
-        <v>2</v>
-      </c>
-      <c r="O17" s="12">
-        <v>3</v>
-      </c>
-      <c r="P17" s="13">
-        <v>4</v>
+      <c r="H17" s="10">
+        <v>2000</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C18" s="6" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="12">
-        <f>-4*P41</f>
-        <v>-4000</v>
+        <v>-4</v>
       </c>
       <c r="I18" s="13">
-        <f>-2.75*P41</f>
-        <v>-2750</v>
+        <v>-3</v>
       </c>
       <c r="J18" s="13">
-        <f>-1.5*P41</f>
-        <v>-1500</v>
+        <v>-2</v>
       </c>
       <c r="K18" s="13">
-        <f>-0.5*P41</f>
-        <v>-500</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="13">
-        <f>0*P41</f>
         <v>0</v>
       </c>
       <c r="M18" s="12">
-        <f>0.5*P41</f>
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="N18" s="12">
-        <f>1.5*P41</f>
-        <v>1500</v>
+        <v>2</v>
       </c>
       <c r="O18" s="12">
-        <f>2.75*P41</f>
-        <v>2750</v>
+        <v>3</v>
       </c>
       <c r="P18" s="13">
-        <f>4*P41</f>
-        <v>4000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="E19" s="4" t="s">
-        <v>18</v>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="13"/>
+      <c r="H19" s="12">
+        <f>-4*P42</f>
+        <v>-4000</v>
+      </c>
+      <c r="I19" s="13">
+        <f>-2.75*P42</f>
+        <v>-2750</v>
+      </c>
+      <c r="J19" s="13">
+        <f>-1.5*P42</f>
+        <v>-1500</v>
+      </c>
+      <c r="K19" s="13">
+        <f>-0.5*P42</f>
+        <v>-500</v>
+      </c>
+      <c r="L19" s="13">
+        <f>0*P42</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="12">
+        <f>0.5*P42</f>
+        <v>500</v>
+      </c>
+      <c r="N19" s="12">
+        <f>1.5*P42</f>
+        <v>1500</v>
+      </c>
+      <c r="O19" s="12">
+        <f>2.75*P42</f>
+        <v>2750</v>
+      </c>
+      <c r="P19" s="13">
+        <f>4*P42</f>
+        <v>4000</v>
+      </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
+      <c r="A20" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="B20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="E20" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
-      <c r="H20" s="10">
-        <v>2000</v>
+      <c r="H20" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="13"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
-      <c r="H21" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I21" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J21" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K21" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L21" s="13">
-        <v>0</v>
-      </c>
-      <c r="M21" s="12">
-        <v>1</v>
-      </c>
-      <c r="N21" s="12">
-        <v>2</v>
-      </c>
-      <c r="O21" s="12">
-        <v>3</v>
-      </c>
-      <c r="P21" s="13">
-        <v>4</v>
-      </c>
+      <c r="H21" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C22" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="12">
-        <f>-4*P45</f>
-        <v>-4000</v>
+        <v>-4</v>
       </c>
       <c r="I22" s="13">
-        <f>-2.75*P45</f>
-        <v>-2750</v>
+        <v>-3</v>
       </c>
       <c r="J22" s="13">
-        <f>-1.5*P45</f>
-        <v>-1500</v>
+        <v>-2</v>
       </c>
       <c r="K22" s="13">
-        <f>-0.5*P45</f>
-        <v>-500</v>
+        <v>-1</v>
       </c>
       <c r="L22" s="13">
-        <f>0*P45</f>
         <v>0</v>
       </c>
       <c r="M22" s="12">
-        <f>0.5*P45</f>
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="N22" s="12">
-        <f>1.5*P45</f>
-        <v>1500</v>
+        <v>2</v>
       </c>
       <c r="O22" s="12">
-        <f>2.75*P45</f>
-        <v>2750</v>
+        <v>3</v>
       </c>
       <c r="P22" s="13">
-        <f>4*P45</f>
-        <v>4000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="E23" s="4" t="s">
-        <v>18</v>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="13"/>
+      <c r="H23" s="12">
+        <f>-4*P46</f>
+        <v>-4000</v>
+      </c>
+      <c r="I23" s="13">
+        <f>-2.75*P46</f>
+        <v>-2750</v>
+      </c>
+      <c r="J23" s="13">
+        <f>-1.5*P46</f>
+        <v>-1500</v>
+      </c>
+      <c r="K23" s="13">
+        <f>-0.5*P46</f>
+        <v>-500</v>
+      </c>
+      <c r="L23" s="13">
+        <f>0*P46</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="12">
+        <f>0.5*P46</f>
+        <v>500</v>
+      </c>
+      <c r="N23" s="12">
+        <f>1.5*P46</f>
+        <v>1500</v>
+      </c>
+      <c r="O23" s="12">
+        <f>2.75*P46</f>
+        <v>2750</v>
+      </c>
+      <c r="P23" s="13">
+        <f>4*P46</f>
+        <v>4000</v>
+      </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
+      <c r="A24" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="B24" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="E24" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="10">
-        <v>2000</v>
-      </c>
+      <c r="H24" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="13"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I25" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J25" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K25" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L25" s="13">
-        <v>0</v>
-      </c>
-      <c r="M25" s="12">
-        <v>1</v>
-      </c>
-      <c r="N25" s="12">
-        <v>2</v>
-      </c>
-      <c r="O25" s="12">
-        <v>3</v>
-      </c>
-      <c r="P25" s="13">
-        <v>4</v>
+      <c r="H25" s="10">
+        <v>2000</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
+      <c r="B26" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C26" s="6" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="12">
-        <f>-4*P49</f>
-        <v>-4000</v>
+        <v>-4</v>
       </c>
       <c r="I26" s="13">
-        <f>-2.75*P49</f>
-        <v>-2750</v>
+        <v>-3</v>
       </c>
       <c r="J26" s="13">
-        <f>-1.5*P49</f>
-        <v>-1500</v>
+        <v>-2</v>
       </c>
       <c r="K26" s="13">
-        <f>-0.5*P49</f>
-        <v>-500</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="13">
-        <f>0*P49</f>
         <v>0</v>
       </c>
       <c r="M26" s="12">
-        <f>0.5*P49</f>
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="N26" s="12">
-        <f>1.5*P49</f>
-        <v>1500</v>
+        <v>2</v>
       </c>
       <c r="O26" s="12">
-        <f>2.75*P49</f>
-        <v>2750</v>
+        <v>3</v>
       </c>
       <c r="P26" s="13">
-        <f>4*P49</f>
-        <v>4000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="E27" s="4" t="s">
-        <v>18</v>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="H27" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="13"/>
+      <c r="H27" s="12">
+        <f>-4*P50</f>
+        <v>-4000</v>
+      </c>
+      <c r="I27" s="13">
+        <f>-2.75*P50</f>
+        <v>-2750</v>
+      </c>
+      <c r="J27" s="13">
+        <f>-1.5*P50</f>
+        <v>-1500</v>
+      </c>
+      <c r="K27" s="13">
+        <f>-0.5*P50</f>
+        <v>-500</v>
+      </c>
+      <c r="L27" s="13">
+        <f>0*P50</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="12">
+        <f>0.5*P50</f>
+        <v>500</v>
+      </c>
+      <c r="N27" s="12">
+        <f>1.5*P50</f>
+        <v>1500</v>
+      </c>
+      <c r="O27" s="12">
+        <f>2.75*P50</f>
+        <v>2750</v>
+      </c>
+      <c r="P27" s="13">
+        <f>4*P50</f>
+        <v>4000</v>
+      </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
+      <c r="A28" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="B28" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="E28" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="10">
-        <v>2000</v>
+      <c r="H28" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="13"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="12">
-        <v>-4</v>
-      </c>
-      <c r="I29" s="13">
-        <v>-3</v>
-      </c>
-      <c r="J29" s="13">
-        <v>-2</v>
-      </c>
-      <c r="K29" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L29" s="13">
-        <v>0</v>
-      </c>
-      <c r="M29" s="12">
-        <v>1</v>
-      </c>
-      <c r="N29" s="12">
-        <v>2</v>
-      </c>
-      <c r="O29" s="12">
-        <v>3</v>
-      </c>
-      <c r="P29" s="13">
-        <v>4</v>
-      </c>
+      <c r="H29" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
+      <c r="B30" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="C30" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="12">
-        <f>-4*P53</f>
+        <v>-4</v>
+      </c>
+      <c r="I30" s="13">
+        <v>-3</v>
+      </c>
+      <c r="J30" s="13">
+        <v>-2</v>
+      </c>
+      <c r="K30" s="13">
+        <v>-1</v>
+      </c>
+      <c r="L30" s="13">
+        <v>0</v>
+      </c>
+      <c r="M30" s="12">
+        <v>1</v>
+      </c>
+      <c r="N30" s="12">
+        <v>2</v>
+      </c>
+      <c r="O30" s="12">
+        <v>3</v>
+      </c>
+      <c r="P30" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="12">
+        <f>-4*P54</f>
         <v>-4000</v>
       </c>
-      <c r="I30" s="13">
-        <f>-2.75*P53</f>
+      <c r="I31" s="13">
+        <f>-2.75*P54</f>
         <v>-2750</v>
       </c>
-      <c r="J30" s="13">
-        <f>-1.5*P53</f>
+      <c r="J31" s="13">
+        <f>-1.5*P54</f>
         <v>-1500</v>
       </c>
-      <c r="K30" s="13">
-        <f>-0.5*P53</f>
+      <c r="K31" s="13">
+        <f>-0.5*P54</f>
         <v>-500</v>
       </c>
-      <c r="L30" s="13">
-        <f>0*P53</f>
+      <c r="L31" s="13">
+        <f>0*P54</f>
         <v>0</v>
       </c>
-      <c r="M30" s="12">
-        <f>0.5*P53</f>
+      <c r="M31" s="12">
+        <f>0.5*P54</f>
         <v>500</v>
       </c>
-      <c r="N30" s="12">
-        <f>1.5*P53</f>
+      <c r="N31" s="12">
+        <f>1.5*P54</f>
         <v>1500</v>
       </c>
-      <c r="O30" s="12">
-        <f>2.75*P53</f>
+      <c r="O31" s="12">
+        <f>2.75*P54</f>
         <v>2750</v>
       </c>
-      <c r="P30" s="13">
-        <f>4*P53</f>
+      <c r="P31" s="13">
+        <f>4*P54</f>
         <v>4000</v>
       </c>
     </row>
-    <row r="33" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P33" s="4">
+    <row r="34" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P34" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P37" s="4">
+    <row r="38" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P38" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="41" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P41" s="4">
+    <row r="42" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P42" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="45" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P45" s="4">
+    <row r="46" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P46" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="49" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P49" s="4">
+    <row r="50" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P50" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="53" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P53" s="4">
+    <row r="54" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P54" s="4">
         <v>1000</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:C10 B12:C30 A21 A29">
+  <conditionalFormatting sqref="B9:C11 B13:C31 A22 A30">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
